--- a/public/smeta-dushevaya-depo-samara-2026.xlsx
+++ b/public/smeta-dushevaya-depo-samara-2026.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,10 +146,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -556,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Основание: ТЗ-36-26-ПО-2026. Регион: г. Самара. Уровень цен: октябрь 2026 г., текущие рыночные цены</t>
+          <t>Основание: ТЗ-36-26-ПО-2026. Регион: г. Самара. Уровень цен: октябрь 2026 г., с учётом роста стоимости работ и материалов (+20%)</t>
         </is>
       </c>
     </row>
@@ -671,7 +673,7 @@
         <v>22.2</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0</v>
@@ -710,7 +712,7 @@
         <v>22.2</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>0</v>
@@ -749,10 +751,10 @@
         <v>22.2</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G11" s="10">
         <f>D11*E11</f>
@@ -792,10 +794,10 @@
         <v>22.2</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G12" s="10">
         <f>D12*E12</f>
@@ -835,10 +837,10 @@
         <v>22.2</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>980</v>
+        <v>1180</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="G13" s="10">
         <f>D13*E13</f>
@@ -878,10 +880,10 @@
         <v>22.2</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G14" s="10">
         <f>D14*E14</f>
@@ -921,10 +923,10 @@
         <v>22.2</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G15" s="10">
         <f>D15*E15</f>
@@ -964,10 +966,10 @@
         <v>22.2</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="G16" s="10">
         <f>D16*E16</f>
@@ -1023,7 +1025,7 @@
         <v>6.18</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>0</v>
@@ -1066,7 +1068,7 @@
         <v>6.18</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>0</v>
@@ -1105,10 +1107,10 @@
         <v>6.18</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G20" s="10">
         <f>D20*E20</f>
@@ -1148,10 +1150,10 @@
         <v>6.18</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G21" s="10">
         <f>D21*E21</f>
@@ -1187,10 +1189,10 @@
         <v>6.18</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1180</v>
+        <v>1420</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="G22" s="10">
         <f>D22*E22</f>
@@ -1226,10 +1228,10 @@
         <v>13</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G23" s="10">
         <f>D23*E23</f>
@@ -1269,10 +1271,10 @@
         <v>6.18</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>550</v>
+        <v>660</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G24" s="10">
         <f>D24*E24</f>
@@ -1308,10 +1310,10 @@
         <v>6.18</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G25" s="10">
         <f>D25*E25</f>
@@ -1347,10 +1349,10 @@
         <v>6.18</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="G26" s="10">
         <f>D26*E26</f>
@@ -1386,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>3800</v>
+        <v>4560</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="G27" s="10">
         <f>D27*E27</f>
@@ -1445,7 +1447,7 @@
         <v>56.55</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
@@ -1484,7 +1486,7 @@
         <v>56.55</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0</v>
@@ -1523,10 +1525,10 @@
         <v>56.55</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G31" s="10">
         <f>D31*E31</f>
@@ -1562,7 +1564,7 @@
         <v>56.55</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F32" s="10" t="n">
         <v>0</v>
@@ -1601,10 +1603,10 @@
         <v>56.55</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G33" s="10">
         <f>D33*E33</f>
@@ -1640,10 +1642,10 @@
         <v>56.55</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="G34" s="10">
         <f>D34*E34</f>
@@ -1683,10 +1685,10 @@
         <v>56.55</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="G35" s="10">
         <f>D35*E35</f>
@@ -1726,10 +1728,10 @@
         <v>56.55</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G36" s="10">
         <f>D36*E36</f>
@@ -1765,10 +1767,10 @@
         <v>56.55</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>1850</v>
+        <v>2220</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>1350</v>
+        <v>1620</v>
       </c>
       <c r="G37" s="10">
         <f>D37*E37</f>
@@ -1808,10 +1810,10 @@
         <v>1</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G38" s="10">
         <f>D38*E38</f>
@@ -1867,7 +1869,7 @@
         <v>24</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>0</v>
@@ -1906,7 +1908,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
@@ -1945,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>3200</v>
+        <v>3840</v>
       </c>
       <c r="F42" s="10" t="n">
         <v>0</v>
@@ -1988,10 +1990,10 @@
         <v>28</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>560</v>
+        <v>670</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>560</v>
+        <v>670</v>
       </c>
       <c r="G43" s="10">
         <f>D43*E43</f>
@@ -2031,10 +2033,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1080</v>
+        <v>1300</v>
       </c>
       <c r="G44" s="10">
         <f>D44*E44</f>
@@ -2074,10 +2076,10 @@
         <v>24</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>2250</v>
+        <v>2700</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="G45" s="10">
         <f>D45*E45</f>
@@ -2133,10 +2135,10 @@
         <v>12</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G47" s="10">
         <f>D47*E47</f>
@@ -2172,10 +2174,10 @@
         <v>1.8</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="G48" s="10">
         <f>D48*E48</f>
@@ -2215,10 +2217,10 @@
         <v>12</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>3600</v>
+        <v>4320</v>
       </c>
       <c r="G49" s="10">
         <f>D49*E49</f>
@@ -2258,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G50" s="10">
         <f>D50*E50</f>
@@ -2313,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="F52" s="10" t="n">
         <v>0</v>
@@ -2352,10 +2354,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>9500</v>
+        <v>11400</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>39000</v>
+        <v>46800</v>
       </c>
       <c r="G53" s="10">
         <f>D53*E53</f>
@@ -2411,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
@@ -2450,10 +2452,10 @@
         <v>10</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>4200</v>
+        <v>5040</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>11500</v>
+        <v>13800</v>
       </c>
       <c r="G56" s="10">
         <f>D56*E56</f>
@@ -2493,10 +2495,10 @@
         <v>8</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>2300</v>
+        <v>2760</v>
       </c>
       <c r="G57" s="10">
         <f>D57*E57</f>
@@ -2536,10 +2538,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>4200</v>
+        <v>5040</v>
       </c>
       <c r="G58" s="10">
         <f>D58*E58</f>
@@ -2575,10 +2577,10 @@
         <v>2</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>1300</v>
+        <v>1560</v>
       </c>
       <c r="G59" s="10">
         <f>D59*E59</f>
@@ -2630,7 +2632,7 @@
         <v>8</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
@@ -2669,10 +2671,10 @@
         <v>8</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>3600</v>
+        <v>4320</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>9800</v>
+        <v>11760</v>
       </c>
       <c r="G62" s="10">
         <f>D62*E62</f>
@@ -2712,7 +2714,7 @@
         <v>2.9</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
@@ -2751,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="F64" s="10" t="n">
         <v>0</v>
@@ -2790,10 +2792,10 @@
         <v>2</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>4600</v>
+        <v>5520</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>4800</v>
+        <v>5760</v>
       </c>
       <c r="G65" s="10">
         <f>D65*E65</f>
@@ -2833,10 +2835,10 @@
         <v>1.5</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G66" s="10">
         <f>D66*E66</f>
@@ -2872,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G67" s="10">
         <f>D67*E67</f>
@@ -2911,10 +2913,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G68" s="10">
         <f>D68*E68</f>
@@ -2954,10 +2956,10 @@
         <v>28</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G69" s="10">
         <f>D69*E69</f>
@@ -2993,10 +2995,10 @@
         <v>30</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>530</v>
+        <v>640</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G70" s="10">
         <f>D70*E70</f>
@@ -3032,10 +3034,10 @@
         <v>2</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G71" s="10">
         <f>D71*E71</f>
@@ -3075,10 +3077,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>1050</v>
+        <v>1260</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G72" s="10">
         <f>D72*E72</f>
@@ -3114,10 +3116,10 @@
         <v>8</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G73" s="10">
         <f>D73*E73</f>
@@ -3153,10 +3155,10 @@
         <v>2</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G74" s="10">
         <f>D74*E74</f>
@@ -3192,10 +3194,10 @@
         <v>6</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G75" s="10">
         <f>D75*E75</f>
@@ -3231,10 +3233,10 @@
         <v>13</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>820</v>
+        <v>980</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G76" s="10">
         <f>D76*E76</f>
@@ -3270,10 +3272,10 @@
         <v>3</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G77" s="10">
         <f>D77*E77</f>
@@ -3309,10 +3311,10 @@
         <v>2</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G78" s="10">
         <f>D78*E78</f>
@@ -3348,10 +3350,10 @@
         <v>2</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G79" s="10">
         <f>D79*E79</f>
@@ -3387,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G80" s="10">
         <f>D80*E80</f>
@@ -3442,7 +3444,7 @@
         <v>5.5</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="F82" s="10" t="n">
         <v>0</v>
@@ -3481,10 +3483,10 @@
         <v>16</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>980</v>
+        <v>1180</v>
       </c>
       <c r="G83" s="10">
         <f>D83*E83</f>
@@ -3524,10 +3526,10 @@
         <v>6.5</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>1050</v>
+        <v>1260</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>1200</v>
+        <v>1440</v>
       </c>
       <c r="G84" s="10">
         <f>D84*E84</f>
@@ -3563,10 +3565,10 @@
         <v>10.5</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>1450</v>
+        <v>1740</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>2100</v>
+        <v>2520</v>
       </c>
       <c r="G85" s="10">
         <f>D85*E85</f>
@@ -3602,10 +3604,10 @@
         <v>2</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>1050</v>
+        <v>1260</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="G86" s="10">
         <f>D86*E86</f>
@@ -3641,10 +3643,10 @@
         <v>1</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2300</v>
+        <v>2760</v>
       </c>
       <c r="G87" s="10">
         <f>D87*E87</f>
@@ -3680,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1900</v>
+        <v>2280</v>
       </c>
       <c r="G88" s="10">
         <f>D88*E88</f>
@@ -3719,10 +3721,10 @@
         <v>8</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="G89" s="10">
         <f>D89*E89</f>
@@ -3758,10 +3760,10 @@
         <v>2</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="G90" s="10">
         <f>D90*E90</f>
@@ -3797,10 +3799,10 @@
         <v>2</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="G91" s="10">
         <f>D91*E91</f>
@@ -3836,10 +3838,10 @@
         <v>2</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="G92" s="10">
         <f>D92*E92</f>
@@ -3875,10 +3877,10 @@
         <v>1</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>6200</v>
+        <v>7440</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>14500</v>
+        <v>17400</v>
       </c>
       <c r="G93" s="10">
         <f>D93*E93</f>
@@ -3918,10 +3920,10 @@
         <v>6</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G94" s="10">
         <f>D94*E94</f>
@@ -3957,10 +3959,10 @@
         <v>10.2</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="G95" s="10">
         <f>D95*E95</f>
@@ -3996,10 +3998,10 @@
         <v>20</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="G96" s="10">
         <f>D96*E96</f>
@@ -4039,10 +4041,10 @@
         <v>1</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="G97" s="10">
         <f>D97*E97</f>
@@ -4078,10 +4080,10 @@
         <v>1</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3600</v>
+        <v>4320</v>
       </c>
       <c r="G98" s="10">
         <f>D98*E98</f>
@@ -4121,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>2100</v>
+        <v>2520</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
@@ -4160,10 +4162,10 @@
         <v>1</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>4600</v>
+        <v>5520</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>4700</v>
+        <v>5640</v>
       </c>
       <c r="G100" s="10">
         <f>D100*E100</f>
@@ -4203,7 +4205,7 @@
         <v>2</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>5200</v>
+        <v>6240</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
@@ -4262,7 +4264,7 @@
         <v>5</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>0</v>
@@ -4301,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>0</v>
@@ -4340,7 +4342,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>0</v>
@@ -4379,10 +4381,10 @@
         <v>10</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="G106" s="10">
         <f>D106*E106</f>
@@ -4422,10 +4424,10 @@
         <v>40</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G107" s="10">
         <f>D107*E107</f>
@@ -4461,10 +4463,10 @@
         <v>40</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="G108" s="10">
         <f>D108*E108</f>
@@ -4500,10 +4502,10 @@
         <v>5</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="G109" s="10">
         <f>D109*E109</f>
@@ -4575,7 +4577,7 @@
         <v>24.6</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F112" s="10" t="n">
         <v>0</v>
@@ -4614,7 +4616,7 @@
         <v>11.6</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F113" s="10" t="n">
         <v>0</v>
@@ -4653,10 +4655,10 @@
         <v>24.6</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G114" s="10">
         <f>D114*E114</f>
@@ -4692,10 +4694,10 @@
         <v>24.6</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G115" s="10">
         <f>D115*E115</f>
@@ -4731,10 +4733,10 @@
         <v>24.6</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>980</v>
+        <v>1180</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="G116" s="10">
         <f>D116*E116</f>
@@ -4770,10 +4772,10 @@
         <v>24.6</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G117" s="10">
         <f>D117*E117</f>
@@ -4809,10 +4811,10 @@
         <v>24.6</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G118" s="10">
         <f>D118*E118</f>
@@ -4848,10 +4850,10 @@
         <v>7.9</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G119" s="10">
         <f>D119*E119</f>
@@ -4887,10 +4889,10 @@
         <v>24.6</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="G120" s="10">
         <f>D120*E120</f>
@@ -4946,7 +4948,7 @@
         <v>12.2</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F122" s="10" t="n">
         <v>0</v>
@@ -4985,7 +4987,7 @@
         <v>28.2</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="F123" s="10" t="n">
         <v>0</v>
@@ -5024,7 +5026,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F124" s="10" t="n">
         <v>0</v>
@@ -5063,10 +5065,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G125" s="10">
         <f>D125*E125</f>
@@ -5102,10 +5104,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>820</v>
+        <v>980</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="G126" s="10">
         <f>D126*E126</f>
@@ -5141,10 +5143,10 @@
         <v>40.4</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G127" s="10">
         <f>D127*E127</f>
@@ -5180,10 +5182,10 @@
         <v>40.4</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="G128" s="10">
         <f>D128*E128</f>
@@ -5219,10 +5221,10 @@
         <v>50.1</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G129" s="10">
         <f>D129*E129</f>
@@ -5258,10 +5260,10 @@
         <v>41</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G130" s="10">
         <f>D130*E130</f>
@@ -5297,10 +5299,10 @@
         <v>37.8</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="G131" s="10">
         <f>D131*E131</f>
@@ -5336,10 +5338,10 @@
         <v>37.8</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G132" s="10">
         <f>D132*E132</f>
@@ -5375,10 +5377,10 @@
         <v>12.2</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>1850</v>
+        <v>2220</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>1350</v>
+        <v>1620</v>
       </c>
       <c r="G133" s="10">
         <f>D133*E133</f>
@@ -5414,10 +5416,10 @@
         <v>37.9</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G134" s="10">
         <f>D134*E134</f>
@@ -5469,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>3200</v>
+        <v>3840</v>
       </c>
       <c r="F136" s="10" t="n">
         <v>0</v>
@@ -5508,10 +5510,10 @@
         <v>1</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>14500</v>
+        <v>17400</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>78000</v>
+        <v>93600</v>
       </c>
       <c r="G137" s="10">
         <f>D137*E137</f>
@@ -5551,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>0</v>
@@ -5590,10 +5592,10 @@
         <v>1</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>9500</v>
+        <v>11400</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>41000</v>
+        <v>49200</v>
       </c>
       <c r="G139" s="10">
         <f>D139*E139</f>
@@ -5645,7 +5647,7 @@
         <v>3.2</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F141" s="10" t="n">
         <v>0</v>
@@ -5684,7 +5686,7 @@
         <v>3</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F142" s="10" t="n">
         <v>0</v>
@@ -5723,7 +5725,7 @@
         <v>7</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F143" s="10" t="n">
         <v>0</v>
@@ -5762,7 +5764,7 @@
         <v>16</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F144" s="10" t="n">
         <v>0</v>
@@ -5801,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="F145" s="10" t="n">
         <v>0</v>
@@ -5840,10 +5842,10 @@
         <v>2</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G146" s="10">
         <f>D146*E146</f>
@@ -5879,10 +5881,10 @@
         <v>2</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="G147" s="10">
         <f>D147*E147</f>
@@ -5918,10 +5920,10 @@
         <v>6</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G148" s="10">
         <f>D148*E148</f>
@@ -5957,10 +5959,10 @@
         <v>2</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G149" s="10">
         <f>D149*E149</f>
@@ -5996,10 +5998,10 @@
         <v>6</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G150" s="10">
         <f>D150*E150</f>
@@ -6035,10 +6037,10 @@
         <v>2</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G151" s="10">
         <f>D151*E151</f>
@@ -6090,10 +6092,10 @@
         <v>1</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="G153" s="10">
         <f>D153*E153</f>
@@ -6129,10 +6131,10 @@
         <v>1</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1850</v>
+        <v>2220</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="G154" s="10">
         <f>D154*E154</f>
@@ -6168,10 +6170,10 @@
         <v>8</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G155" s="10">
         <f>D155*E155</f>
@@ -6223,7 +6225,7 @@
         <v>2</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F157" s="10" t="n">
         <v>0</v>
@@ -6262,10 +6264,10 @@
         <v>3</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>2900</v>
+        <v>3480</v>
       </c>
       <c r="G158" s="10">
         <f>D158*E158</f>
@@ -6301,7 +6303,7 @@
         <v>42</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F159" s="10" t="n">
         <v>0</v>
@@ -6340,10 +6342,10 @@
         <v>16</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="G160" s="10">
         <f>D160*E160</f>
@@ -6379,10 +6381,10 @@
         <v>4</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="G161" s="10">
         <f>D161*E161</f>
@@ -6418,10 +6420,10 @@
         <v>1</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="G162" s="10">
         <f>D162*E162</f>
@@ -6457,10 +6459,10 @@
         <v>2</v>
       </c>
       <c r="E163" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="F163" s="10" t="n">
         <v>160</v>
-      </c>
-      <c r="F163" s="10" t="n">
-        <v>130</v>
       </c>
       <c r="G163" s="10">
         <f>D163*E163</f>
@@ -6496,7 +6498,7 @@
         <v>1.3</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F164" s="10" t="n">
         <v>0</v>
@@ -6535,7 +6537,7 @@
         <v>17</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F165" s="10" t="n">
         <v>20</v>
@@ -6574,7 +6576,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F166" s="10" t="n">
         <v>0</v>
@@ -6613,7 +6615,7 @@
         <v>4</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F167" s="10" t="n">
         <v>0</v>
@@ -6652,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F168" s="10" t="n">
         <v>0</v>
@@ -6691,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>1550</v>
+        <v>1860</v>
       </c>
       <c r="F169" s="10" t="n">
         <v>0</v>
@@ -6711,7 +6713,7 @@
       <c r="J169" s="9" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="7" t="inlineStr">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>4.2.5. АПС</t>
         </is>
@@ -6746,7 +6748,7 @@
         <v>17</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F171" s="10" t="n">
         <v>20</v>
@@ -6785,7 +6787,7 @@
         <v>3</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F172" s="10" t="n">
         <v>20</v>
@@ -6824,7 +6826,7 @@
         <v>2</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="F173" s="10" t="n">
         <v>0</v>
@@ -6867,10 +6869,10 @@
         <v>40</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G174" s="10">
         <f>D174*E174</f>
@@ -6938,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>28000</v>
+        <v>33600</v>
       </c>
       <c r="F177" s="10" t="n">
         <v>0</v>
@@ -6981,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>18000</v>
+        <v>21600</v>
       </c>
       <c r="F178" s="10" t="n">
         <v>0</v>
@@ -7024,7 +7026,7 @@
         <v>1</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>14000</v>
+        <v>16800</v>
       </c>
       <c r="F179" s="10" t="n">
         <v>0</v>
@@ -7067,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="F180" s="10" t="n">
         <v>0</v>
@@ -7110,7 +7112,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>2200</v>
+        <v>2640</v>
       </c>
       <c r="F181" s="10" t="n">
         <v>0</v>
@@ -7156,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>16000</v>
+        <v>19200</v>
       </c>
       <c r="G182" s="10">
         <f>D182*E182</f>
@@ -7196,7 +7198,7 @@
         <v>1</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>16000</v>
+        <v>19200</v>
       </c>
       <c r="F183" s="10" t="n">
         <v>0</v>
@@ -7239,10 +7241,10 @@
         <v>1</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>8000</v>
+        <v>9600</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="G184" s="10">
         <f>D184*E184</f>
@@ -7298,7 +7300,7 @@
       <c r="D187" s="6" t="n"/>
       <c r="E187" s="6" t="n"/>
       <c r="F187" s="6" t="n"/>
-      <c r="G187" s="14" t="n"/>
+      <c r="G187" s="6" t="n"/>
       <c r="H187" s="14">
         <f>H186*0.04</f>
         <v/>
@@ -7324,7 +7326,7 @@
         <f>G186*0.12</f>
         <v/>
       </c>
-      <c r="H188" s="14" t="n"/>
+      <c r="H188" s="6" t="n"/>
       <c r="I188" s="14">
         <f>G188</f>
         <v/>
@@ -7342,8 +7344,8 @@
       <c r="D189" s="6" t="n"/>
       <c r="E189" s="6" t="n"/>
       <c r="F189" s="6" t="n"/>
-      <c r="G189" s="14" t="n"/>
-      <c r="H189" s="14" t="n"/>
+      <c r="G189" s="6" t="n"/>
+      <c r="H189" s="6" t="n"/>
       <c r="I189" s="14">
         <f>(I186+I187+I188)*0.08</f>
         <v/>
@@ -7356,18 +7358,18 @@
           <t>ИТОГО без НДС</t>
         </is>
       </c>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="6" t="n"/>
-      <c r="D190" s="6" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="6" t="n"/>
+      <c r="B190" s="16" t="n"/>
+      <c r="C190" s="16" t="n"/>
+      <c r="D190" s="16" t="n"/>
+      <c r="E190" s="16" t="n"/>
+      <c r="F190" s="16" t="n"/>
       <c r="G190" s="16" t="n"/>
       <c r="H190" s="16" t="n"/>
-      <c r="I190" s="16">
+      <c r="I190" s="17">
         <f>I186+I187+I188+I189</f>
         <v/>
       </c>
-      <c r="J190" s="6" t="n"/>
+      <c r="J190" s="16" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
@@ -7380,8 +7382,8 @@
       <c r="D191" s="6" t="n"/>
       <c r="E191" s="6" t="n"/>
       <c r="F191" s="6" t="n"/>
-      <c r="G191" s="14" t="n"/>
-      <c r="H191" s="14" t="n"/>
+      <c r="G191" s="6" t="n"/>
+      <c r="H191" s="6" t="n"/>
       <c r="I191" s="14">
         <f>I190*0.22</f>
         <v/>
@@ -7389,77 +7391,77 @@
       <c r="J191" s="6" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="17" t="inlineStr">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>ВСЕГО с НДС 22%</t>
         </is>
       </c>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="6" t="n"/>
-      <c r="D192" s="6" t="n"/>
-      <c r="E192" s="6" t="n"/>
-      <c r="F192" s="6" t="n"/>
-      <c r="G192" s="18" t="n"/>
-      <c r="H192" s="18" t="n"/>
-      <c r="I192" s="18">
+      <c r="B192" s="19" t="n"/>
+      <c r="C192" s="19" t="n"/>
+      <c r="D192" s="19" t="n"/>
+      <c r="E192" s="19" t="n"/>
+      <c r="F192" s="19" t="n"/>
+      <c r="G192" s="19" t="n"/>
+      <c r="H192" s="19" t="n"/>
+      <c r="I192" s="20">
         <f>I190+I191</f>
         <v/>
       </c>
-      <c r="J192" s="6" t="n"/>
+      <c r="J192" s="19" t="n"/>
     </row>
     <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="19" t="inlineStr">
+      <c r="A194" s="21" t="inlineStr">
         <is>
           <t>Примечания и допущения:</t>
         </is>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1">
-      <c r="A195" s="20" t="inlineStr">
-        <is>
-          <t>1. Цены — рыночный уровень г. Самара на октябрь 2026 г. Цвет/фактура плитки, краски, тип перегородок, дверей, светильников — по согласованию с Заказчиком (ТЗ); при выборе другой ценовой категории материалов итог изменится.</t>
+      <c r="A195" s="22" t="inlineStr">
+        <is>
+          <t>1. Цены — рыночный уровень г. Самара на октябрь 2026 г., повышены на 20% к предыдущей редакции с учётом роста стоимости работ и материалов. Штукатурка стен — не ниже 600 ₽/м² за работу. Цвет/фактура плитки, краски, тип перегородок, дверей, светильников — по согласованию с Заказчиком.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="20" t="inlineStr">
+      <c r="A196" s="22" t="inlineStr">
         <is>
           <t>2. Двери ПВХ с сэндвич-панелями, доводчиками и откосами изготавливаются под заказ; размеры уточняются замером (ТЗ п.4.1.1.40, 4.2.1.24, 4.2.1.26).</t>
         </is>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="20" t="inlineStr">
-        <is>
-          <t>3. Душевые перегородки (п.4.1.1.42) — ПВХ-профиль; в стоимость включены подставки 8 шт., зеркала 2 шт., вешалки 2 шт. по примечанию ТЗ.</t>
+      <c r="A197" s="22" t="inlineStr">
+        <is>
+          <t>3. Душевые перегородки (п.4.1.1.42) — ПВХ-профиль; включены подставки 8 шт., зеркала 2 шт., вешалки 2 шт. по примечанию ТЗ.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1">
-      <c r="A198" s="20" t="inlineStr">
-        <is>
-          <t>4. В ТЗ п.4.2.2.11 дублирует п.4.2.2.6 (муфта 20×1/2" × 2 шт.) — включено как указано в ТЗ, рекомендуется уточнить у Заказчика. Пункт 4.1.3.11 в ТЗ отсутствует. Пункт «4.1.1.13» в разделе 4.2 — опечатка ТЗ, учтён как 4.2.1.13.</t>
+      <c r="A198" s="22" t="inlineStr">
+        <is>
+          <t>4. В ТЗ п.4.2.2.11 дублирует п.4.2.2.6 — включено как указано, рекомендуется уточнить. Пункт 4.1.3.11 в ТЗ отсутствует. «4.1.1.13» в разделе 4.2 — опечатка ТЗ, учтён как 4.2.1.13.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="30" customHeight="1">
-      <c r="A199" s="20" t="inlineStr">
-        <is>
-          <t>5. Включены обязательные по ТЗ затраты: ППР/ПОБ, исполнительная документация (2 экз.), электроизмерения, сортировка и сдача лома, вывоз и утилизация мусора, ежедневная уборка, СИЗ (разделы 5–6 ТЗ). Согласно п.5.7 неучтённые работы выполняются за счёт подрядчика.</t>
+      <c r="A199" s="22" t="inlineStr">
+        <is>
+          <t>5. Включены обязательные по ТЗ затраты: ППР/ПОБ, исполнительная документация (2 экз.), электроизмерения, сортировка и сдача лома, вывоз и утилизация мусора, уборка, СИЗ (разделы 5–6 ТЗ).</t>
         </is>
       </c>
     </row>
     <row r="200" ht="30" customHeight="1">
-      <c r="A200" s="20" t="inlineStr">
-        <is>
-          <t>6. Не включено: стоимость получения/наличия СРО (п.5.1), простои по вине Заказчика, работы вне перечня ТЗ.</t>
+      <c r="A200" s="22" t="inlineStr">
+        <is>
+          <t>6. Не включено: стоимость СРО (п.5.1), простои по вине Заказчика, работы вне перечня ТЗ.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="30" customHeight="1">
-      <c r="A201" s="20" t="inlineStr">
-        <is>
-          <t>7. Ставка НДС 22% применяется с 01.01.2026. Если подрядчик на УСН без НДС — к оплате «ИТОГО без НДС».</t>
+      <c r="A201" s="22" t="inlineStr">
+        <is>
+          <t>7. НДС 22% (с 01.01.2026). Если подрядчик на УСН без НДС — к оплате «ИТОГО без НДС».</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7524,27 +7526,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Помещение</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Раздел</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Работа, ₽</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Материалы, ₽</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Всего, ₽</t>
         </is>
@@ -7561,14 +7563,14 @@
           <t>4.1.1. Общестроительные работы — Потолок</t>
         </is>
       </c>
-      <c r="C2" s="22" t="n">
-        <v>55167</v>
-      </c>
-      <c r="D2" s="22" t="n">
-        <v>20646</v>
-      </c>
-      <c r="E2" s="22" t="n">
-        <v>75813</v>
+      <c r="C2" s="24" t="n">
+        <v>66156</v>
+      </c>
+      <c r="D2" s="24" t="n">
+        <v>25086</v>
+      </c>
+      <c r="E2" s="24" t="n">
+        <v>91242</v>
       </c>
     </row>
     <row r="3">
@@ -7582,14 +7584,14 @@
           <t>Ригель на потолке</t>
         </is>
       </c>
-      <c r="C3" s="22" t="n">
-        <v>24717.3</v>
-      </c>
-      <c r="D3" s="22" t="n">
-        <v>7542.399999999999</v>
-      </c>
-      <c r="E3" s="22" t="n">
-        <v>32259.7</v>
+      <c r="C3" s="24" t="n">
+        <v>29736.2</v>
+      </c>
+      <c r="D3" s="24" t="n">
+        <v>9163.4</v>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>38899.6</v>
       </c>
     </row>
     <row r="4">
@@ -7603,14 +7605,14 @@
           <t>Стены</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n">
-        <v>237130.75</v>
-      </c>
-      <c r="D4" s="22" t="n">
-        <v>128618.5</v>
-      </c>
-      <c r="E4" s="22" t="n">
-        <v>365749.25</v>
+      <c r="C4" s="24" t="n">
+        <v>284104.5</v>
+      </c>
+      <c r="D4" s="24" t="n">
+        <v>154681.5</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>438786</v>
       </c>
     </row>
     <row r="5">
@@ -7624,14 +7626,14 @@
           <t>Полы</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>119920</v>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>78800</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>198720</v>
+      <c r="C5" s="24" t="n">
+        <v>143800</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>94600</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>238400</v>
       </c>
     </row>
     <row r="6">
@@ -7645,14 +7647,14 @@
           <t>Прочее</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>28620</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>49410</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>78030</v>
+      <c r="C6" s="24" t="n">
+        <v>34296</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>59268</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>93564</v>
       </c>
     </row>
     <row r="7">
@@ -7666,14 +7668,14 @@
           <t>Двери</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>12100</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>39000</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>51100</v>
+      <c r="C7" s="24" t="n">
+        <v>14520</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>46800</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>61320</v>
       </c>
     </row>
     <row r="8">
@@ -7687,14 +7689,14 @@
           <t>Перегородки в душевой</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>63300</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>144400</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>207700</v>
+      <c r="C8" s="24" t="n">
+        <v>75960</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>173280</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>249240</v>
       </c>
     </row>
     <row r="9">
@@ -7708,14 +7710,14 @@
           <t>4.1.2. Водоснабжение и канализация</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>124082</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>97567</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>221649</v>
+      <c r="C9" s="24" t="n">
+        <v>149034</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>116978</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>266012</v>
       </c>
     </row>
     <row r="10">
@@ -7729,14 +7731,14 @@
           <t>4.1.3. Вентиляция</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
-        <v>94197</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>103468</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>197665</v>
+      <c r="C10" s="24" t="n">
+        <v>112830</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>124274</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>237104</v>
       </c>
     </row>
     <row r="11">
@@ -7750,14 +7752,14 @@
           <t>4.1.4. Электроснабжение</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
-        <v>34800</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>36200</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>71000</v>
+      <c r="C11" s="24" t="n">
+        <v>41800</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>43350</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>85150</v>
       </c>
     </row>
     <row r="12">
@@ -7771,14 +7773,14 @@
           <t>4.2.1. Общестроительные работы — Потолок</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
-        <v>63337</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>21928</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>85265</v>
+      <c r="C12" s="24" t="n">
+        <v>75984</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>26593</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>102577</v>
       </c>
     </row>
     <row r="13">
@@ -7792,14 +7794,14 @@
           <t>Стены</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
-        <v>124710</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>53422.5</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>178132.5</v>
+      <c r="C13" s="24" t="n">
+        <v>149463</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>64265</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>213728</v>
       </c>
     </row>
     <row r="14">
@@ -7813,14 +7815,14 @@
           <t>Двери</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
-        <v>29800</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>119000</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>148800</v>
+      <c r="C14" s="24" t="n">
+        <v>35760</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>142800</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>178560</v>
       </c>
     </row>
     <row r="15">
@@ -7834,14 +7836,14 @@
           <t>4.2.2. Водоснабжение и канализация</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
-        <v>17474</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>3360</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>20834</v>
+      <c r="C15" s="24" t="n">
+        <v>20830</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="16">
@@ -7855,14 +7857,14 @@
           <t>4.2.3. Прочее</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
-        <v>8540</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>1260</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>9800</v>
+      <c r="C16" s="24" t="n">
+        <v>10280</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>11800</v>
       </c>
     </row>
     <row r="17">
@@ -7876,56 +7878,35 @@
           <t>4.2.4. Электроснабжение</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
-        <v>33126</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>21780</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>54906</v>
+      <c r="C17" s="24" t="n">
+        <v>51470</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>27320</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>78790</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ПОМЕЩЕНИЕ № 2 (УМЫВАЛЬНИК), 24,6 м², h=2,9 м</t>
+          <t>ЗАТРАТЫ ПО ТРЕБОВАНИЯМ ТЗ (раздел 5–6)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>4.2.5. АПС</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>9990</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>10990</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ЗАТРАТЫ ПО ТРЕБОВАНИЯМ ТЗ (раздел 5–6)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
           <t>Сопутствующие работы, обязательные по ТЗ</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n">
-        <v>109800</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>38000</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>147800</v>
+      <c r="C18" s="24" t="n">
+        <v>131760</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>177360</v>
       </c>
     </row>
   </sheetData>
